--- a/compliance/Gap_Analysis.xlsx
+++ b/compliance/Gap_Analysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kate\OneDrive\Documents\GRC_Risk_Assessment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kate\OneDrive\Documents\GRC_Risk_Assessment\C3-GRC\compliance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{90BDE6D1-5B11-443C-9579-858150CCD221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B057A71F-5A14-4D35-833D-C07C73E3AACB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26520" yWindow="288" windowWidth="17280" windowHeight="8880" xr2:uid="{99CF0CFB-6A08-4B00-ACC3-3B9350E92625}"/>
+    <workbookView xWindow="22944" yWindow="0" windowWidth="14412" windowHeight="12336" xr2:uid="{99CF0CFB-6A08-4B00-ACC3-3B9350E92625}"/>
   </bookViews>
   <sheets>
     <sheet name="Gap Analysis" sheetId="1" r:id="rId1"/>
@@ -36,28 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="130">
-  <si>
-    <t>Data Management</t>
-  </si>
-  <si>
-    <t>Data Leakage Prevention</t>
-  </si>
-  <si>
-    <t>C3-CTL-030</t>
-  </si>
-  <si>
-    <t>C3-GAP-030</t>
-  </si>
-  <si>
-    <t>Information Deletion</t>
-  </si>
-  <si>
-    <t>C3-CTL-029</t>
-  </si>
-  <si>
-    <t>C3-GAP-029</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="111">
   <si>
     <t>Secure Development</t>
   </si>
@@ -65,33 +44,9 @@
     <t>Access to Source Code</t>
   </si>
   <si>
-    <t>C3-CTL-028</t>
-  </si>
-  <si>
-    <t>C3-GAP-028</t>
-  </si>
-  <si>
     <t>Secure Development Life Cycle</t>
   </si>
   <si>
-    <t>C3-CTL-027</t>
-  </si>
-  <si>
-    <t>C3-GAP-027</t>
-  </si>
-  <si>
-    <t>Business Continuity</t>
-  </si>
-  <si>
-    <t>Information Security During Disruption</t>
-  </si>
-  <si>
-    <t>C3-CTL-026</t>
-  </si>
-  <si>
-    <t>C3-GAP-026</t>
-  </si>
-  <si>
     <t>Incident Management</t>
   </si>
   <si>
@@ -104,9 +59,6 @@
     <t>C3-GAP-025</t>
   </si>
   <si>
-    <t>Incident Management Planning</t>
-  </si>
-  <si>
     <t>C3-CTL-024</t>
   </si>
   <si>
@@ -146,12 +98,6 @@
     <t>C3-GAP-021</t>
   </si>
   <si>
-    <t>Cryptography</t>
-  </si>
-  <si>
-    <t>Use of Cryptography</t>
-  </si>
-  <si>
     <t>C3-CTL-020</t>
   </si>
   <si>
@@ -206,12 +152,6 @@
     <t>C3-GAP-015</t>
   </si>
   <si>
-    <t>Physical Security</t>
-  </si>
-  <si>
-    <t>Equipment Siting and Protection</t>
-  </si>
-  <si>
     <t>C3-CTL-014</t>
   </si>
   <si>
@@ -221,18 +161,12 @@
     <t>People</t>
   </si>
   <si>
-    <t>Responsibilities After Termination</t>
-  </si>
-  <si>
     <t>C3-CTL-013</t>
   </si>
   <si>
     <t>C3-GAP-013</t>
   </si>
   <si>
-    <t>Security Awareness Training</t>
-  </si>
-  <si>
     <t>C3-CTL-012</t>
   </si>
   <si>
@@ -251,9 +185,6 @@
     <t>C3-GAP-011</t>
   </si>
   <si>
-    <t>Asset Inventory</t>
-  </si>
-  <si>
     <t>C3-CTL-010</t>
   </si>
   <si>
@@ -275,9 +206,6 @@
     <t>Compliance</t>
   </si>
   <si>
-    <t>Legal &amp; Regulatory Requirements</t>
-  </si>
-  <si>
     <t>C3-CTL-008</t>
   </si>
   <si>
@@ -426,6 +354,21 @@
   </si>
   <si>
     <t>CrochetCrochetCrochet (C3) — Gap Analysis Register</t>
+  </si>
+  <si>
+    <t>Legal, Statutory, Regulatory and Contractual Requirements</t>
+  </si>
+  <si>
+    <t>Inventory of Information and Other Associated Assets</t>
+  </si>
+  <si>
+    <t>Information Security Awareness, Education and Training</t>
+  </si>
+  <si>
+    <t>Responsibilities After Termination or Change of Employment</t>
+  </si>
+  <si>
+    <t>Information Security Incident Management Planning</t>
   </si>
 </sst>
 </file>
@@ -446,11 +389,6 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -489,8 +427,13 @@
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1E293B"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="22">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -505,12 +448,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF3E8FF"/>
-        <bgColor rgb="FFF3E8FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFEEF2F7"/>
         <bgColor rgb="FFEEF2F7"/>
       </patternFill>
@@ -535,12 +472,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFE4E6"/>
-        <bgColor rgb="FFFFE4E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFEE2E2"/>
         <bgColor rgb="FFFEE2E2"/>
       </patternFill>
@@ -559,20 +490,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0FDF4"/>
-        <bgColor rgb="FFF0FDF4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFEDE9FE"/>
         <bgColor rgb="FFEDE9FE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2FE"/>
-        <bgColor rgb="FFE0F2FE"/>
       </patternFill>
     </fill>
     <fill>
@@ -682,75 +601,63 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -972,141 +879,144 @@
   </sheetPr>
   <dimension ref="A1:M33"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="26.109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="22"/>
+      <c r="A1" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="9"/>
     </row>
     <row r="2" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="B2" s="21" t="s">
-        <v>127</v>
-      </c>
-      <c r="C2" s="21" t="s">
-        <v>126</v>
-      </c>
-      <c r="D2" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="E2" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="F2" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="G2" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="H2" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="I2" s="21" t="s">
-        <v>120</v>
-      </c>
-      <c r="J2" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="K2" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="L2" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="M2" s="21" t="s">
-        <v>116</v>
+      <c r="A2" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>114</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>114</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>114</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="F3" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="G3" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="H3" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="I3" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="J3" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="K3" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="L3" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="M3" s="20" t="s">
-        <v>105</v>
+      <c r="A3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
+      <c r="A4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
     </row>
     <row r="5" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>86</v>
+      <c r="A5" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>62</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -1119,40 +1029,40 @@
       <c r="M5" s="1"/>
     </row>
     <row r="6" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
+      <c r="A6" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
     </row>
     <row r="7" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>86</v>
+      <c r="A7" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>62</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -1165,40 +1075,40 @@
       <c r="M7" s="1"/>
     </row>
     <row r="8" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
+      <c r="A8" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
     </row>
     <row r="9" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>86</v>
+      <c r="A9" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>62</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -1211,40 +1121,40 @@
       <c r="M9" s="1"/>
     </row>
     <row r="10" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-    </row>
-    <row r="11" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>78</v>
+      <c r="A10" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+    </row>
+    <row r="11" spans="1:13" ht="22.8" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>55</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -1257,40 +1167,40 @@
       <c r="M11" s="1"/>
     </row>
     <row r="12" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-    </row>
-    <row r="13" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>67</v>
+      <c r="A12" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+    </row>
+    <row r="13" spans="1:13" ht="24" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>45</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
@@ -1302,41 +1212,41 @@
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
-    <row r="14" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-    </row>
-    <row r="15" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>60</v>
+    <row r="14" spans="1:13" ht="24" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+    </row>
+    <row r="15" spans="1:13" ht="22.8" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>40</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
@@ -1348,41 +1258,41 @@
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
     </row>
-    <row r="16" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
+    <row r="16" spans="1:13" ht="22.8" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
     </row>
     <row r="17" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>56</v>
+      <c r="A17" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
@@ -1394,41 +1304,41 @@
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
     </row>
-    <row r="18" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
+    <row r="18" spans="1:13" ht="22.8" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="4"/>
     </row>
     <row r="19" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>40</v>
+      <c r="A19" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
@@ -1441,40 +1351,40 @@
       <c r="M19" s="1"/>
     </row>
     <row r="20" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
+      <c r="A20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="4"/>
     </row>
     <row r="21" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>40</v>
+      <c r="A21" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
@@ -1486,41 +1396,41 @@
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
     </row>
-    <row r="22" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-    </row>
-    <row r="23" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>36</v>
+    <row r="22" spans="1:13" ht="24" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="4"/>
+    </row>
+    <row r="23" spans="1:13" ht="24" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>9</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
@@ -1532,41 +1442,41 @@
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
     </row>
-    <row r="24" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
-    </row>
-    <row r="25" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>25</v>
+    <row r="24" spans="1:13" ht="24" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="4"/>
+    </row>
+    <row r="25" spans="1:13" ht="24" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>3</v>
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
@@ -1578,41 +1488,41 @@
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
     </row>
-    <row r="26" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="6"/>
-      <c r="M26" s="6"/>
-    </row>
-    <row r="27" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>18</v>
+    <row r="26" spans="1:13" ht="24" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="4"/>
+    </row>
+    <row r="27" spans="1:13" ht="24" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>0</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
@@ -1624,143 +1534,73 @@
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
     </row>
-    <row r="28" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
-      <c r="M28" s="6"/>
+    <row r="28" spans="1:13" ht="24" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="4"/>
     </row>
     <row r="29" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>14</v>
-      </c>
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
     </row>
     <row r="30" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="6"/>
-      <c r="M30" s="6"/>
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
     </row>
     <row r="31" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>7</v>
-      </c>
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
     </row>
     <row r="32" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="6"/>
-      <c r="K32" s="6"/>
-      <c r="L32" s="6"/>
-      <c r="M32" s="6"/>
-    </row>
-    <row r="33" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>0</v>
-      </c>
+      <c r="A32" s="4"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+    </row>
+    <row r="33" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
